--- a/tenthousand-cc/tenthousand-cc_5_upgraded_products.xlsx
+++ b/tenthousand-cc/tenthousand-cc_5_upgraded_products.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -160,6 +160,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -531,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -570,35 +571,45 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Current Word Count</t>
+          <t>Feed Word Count (Shopify API)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Live Storefront Words (Theme)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Feed vs Theme Diagnostic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Upgraded Description (Clean Readable Text + Specs)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Current Alt Text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Image Alt Text</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Google Shopping Category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Upgraded Smart Tags</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Live Product URL</t>
         </is>
@@ -622,45 +633,53 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Daily Ripstop Tote | Everyday Performance &amp; Fit</t>
+          <t>Ten Thousand Daily Ripstop Tote Bag | Durable Gym &amp; Travel Carry</t>
         </is>
       </c>
       <c r="E2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>The Daily Ripstop Tote by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginTenthousand Cc (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F2" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
+          <t>Thin copy in feed &amp; store</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Engineered for the uncompromising athlete, our Daily Ripstop Tote offers a rugged solution for transporting your gear from the training floor to the office. This versatile bag combines minimalist design with military-grade durability to withstand your toughest daily commutes.
+Key Features &amp; Benefits
+• Constructed from high-tenacity, tear-resistant ripstop nylon fabric.
+• Reinforced stress points ensure maximum load-bearing capacity for gym equipment.
+• Water-resistant coating protects your belongings from the elements.
+• Internal organization pockets for secure storage of valuables and small items.
+• Minimalist aesthetic that seamlessly transitions from gym to city life.
+Material: 100% Ripstop Nylon | Dimensions: Standard Carry | Weight: Lightweight Performance</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>Daily Ripstop Tote - Tenthousand Cc Official Product View</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>Ten Thousand Daily Ripstop Tote bag in black featuring durable fabric and minimalist logo branding.</t>
         </is>
       </c>
       <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Handbags, Wallets &amp; Cases &gt; Totes</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
+        <is>
+          <t>Accessories, Bags, Tote, Gym Gear, Travel, Ripstop</t>
+        </is>
+      </c>
+      <c r="M2" s="10" t="inlineStr">
         <is>
           <t>https://tenthousand.cc/products/daily-ripstop-tote</t>
         </is>
@@ -684,45 +703,53 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Core Logo Hat | Everyday Performance &amp; Fit</t>
+          <t>Ten Thousand Core Logo Hat | Performance Training Cap</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>The Core Logo Hat by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginTenthousand Cc (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F3" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
+          <t>Thin copy in feed &amp; store</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Stay focused during high-intensity training sessions with a performance cap designed to manage moisture and keep you cool. The Core Logo Hat combines a sleek, athletic silhouette with breathable materials for all-day comfort.
+Key Features &amp; Benefits
+• Moisture-wicking interior sweatband pulls perspiration away from the skin.
+• Lightweight, breathable crown fabric maximizes airflow during exertion.
+• Adjustable snapback closure for a customizable, secure fit.
+• Structure-maintained visor provides consistent coverage and sun protection.
+• Low-profile design minimizes bulk for an unobtrusive training experience.
+Material: Performance Polyester Blend | Fit: Adjustable Snapback | Design: Low Profile</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>Core Logo Hat - Tenthousand Cc Official Product View</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>Ten Thousand Core Logo athletic training hat with adjustable snapback and signature branding.</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing Accessories &gt; Hats</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr">
+        <is>
+          <t>Accessories, Headwear, Hats, Training Gear, Core Collection, Performance</t>
+        </is>
+      </c>
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>https://tenthousand.cc/products/core-logo-hat</t>
         </is>
@@ -746,45 +773,53 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Cotton Bandana - Kettlebell | Everyday Performance &amp; Fit</t>
+          <t>Ten Thousand Kettlebell Cotton Bandana | Versatile Gym Accessory</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>The Cotton Bandana - Kettlebell by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginTenthousand Cc (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F4" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
+          <t>Thin copy in feed &amp; store</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>A classic training staple reimagined, this cotton bandana provides essential moisture management and versatility for every athlete. Whether used to keep sweat at bay or as a quick wrap, its durable construction stands up to daily gym abuse.
+Key Features &amp; Benefits
+• Soft, high-quality cotton construction for superior comfort against the skin.
+• Highly absorbent fabric effectively wicks moisture during heavy lifting.
+• Multi-functional design serves as a head-tie, wristband, or equipment grip.
+• Custom Kettlebell graphic print honors the classic training aesthetic.
+• Easy-care material that withstands repeated washing and intense usage.
+Material: 100% Cotton | Print: Custom Kettlebell Graphic | Size: Standard Square</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>Cotton Bandana - Kettlebell - Tenthousand Cc Official Product View</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>Ten Thousand cotton bandana featuring a kettlebell print graphic in high-contrast ink.</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing Accessories &gt; Bandanas</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>Accessories, Bandana, Kettlebell, Training Essentials, Gym Gear, Limited Edition</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>https://tenthousand.cc/products/tt-bandana</t>
         </is>
@@ -808,45 +843,53 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>YETI® x Ten Thousand Rambler 36oz | Everyday Performance &amp; Fit</t>
+          <t>YETI x Ten Thousand Rambler 36oz Insulated Water Bottle</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>The YETI® x Ten Thousand Rambler 36oz by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginTenthousand Cc (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F5" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
+          <t>Thin copy in feed &amp; store</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Master your hydration with this premium collaboration bottle, featuring legendary YETI insulation to keep your drinks ice-cold during the most grueling sessions. Built for the rugged athlete, it stands as the ultimate companion for gym training and off-grid exploration.
+Key Features &amp; Benefits
+• Double-wall vacuum insulation keeps liquids cold or hot for hours.
+• 18/8 stainless steel construction provides puncture and rust resistance.
+• No-Sweat™ design keeps your hands dry while the bottle remains cold.
+• Leak-resistant Chug Cap allows for quick, effortless hydration flow.
+• Durable dishwasher-safe design makes post-workout cleanup simple.
+Volume: 36 oz | Material: 18/8 Stainless Steel | Compatibility: Dishwasher Safe</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>YETI® x Ten Thousand Rambler 36oz - Tenthousand Cc Official Product View</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>YETI x Ten Thousand Rambler 36oz insulated stainless steel water bottle with co-branded logo.</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Kitchen &amp; Dining &gt; Kitchen Tools &amp; Utensils &gt; Water Bottles</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>Accessories, Yeti, Hydration, Water Bottle, Gym Gear, Collaboration</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>https://tenthousand.cc/products/tt-yeti-water-bottle</t>
         </is>
@@ -870,45 +913,53 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Black | Everyday Performance &amp; Fit</t>
+          <t>Ten Thousand Elite Plus Membership | Black Tier Benefits</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>The Black by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.
-Key Features &amp; Highlights
-• Performance Fabric Blend: Engineered for superior breathability, natural stretch, and all-day comfort.
-• Tailored Precision Silhouette: Modern athletic profile that transitions seamlessly from office to active wear.
-• Reinforced Durability: Double-needle flatlock stitching on high-stress seams prevents warping and fraying.
-• Pre-Shrunk &amp; Easy Care: Maintains original fit, color depth, and soft hand-feel wash after wash.
-Technical Specifications
-Fabric CompositionPremium Cotton &amp; Technical Performance BlendFit ProfileModern Tailored Silhouette (True to Size)Care InstructionsMachine wash cold with like colors, tumble dry lowBrand OriginTenthousand Cc (United States)CraftsmanshipReinforced Seams &amp; Colorfast Finish</t>
-        </is>
+      <c r="F6" s="7" t="n">
+        <v>2</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
+          <t>Thin copy in feed &amp; store</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>Unlock the highest level of athletic performance and community access with our exclusive Elite Plus Black Membership. This premium tier is designed for the dedicated athlete seeking priority service and unique member-only advantages.
+Key Features &amp; Benefits
+• Exclusive early access to limited edition product drops and collaborations.
+• Priority customer service support for all your account needs.
+• Invitations to private, member-only training events and challenges.
+• Enhanced benefits across the entire Ten Thousand ecosystem.
+• Members-only pricing and loyalty rewards for high-frequency training.
+Status: Elite Plus Black | Access: Unlimited Membership | Validity: Annual</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
           <t>Missing / Empty (Not Indexed)</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>Black - Tenthousand Cc Official Product View</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
+          <t>Ten Thousand Elite Plus membership badge icon for Black tier subscribers.</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>Services &gt; Subscriptions &gt; Membership Programs</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>Membership, Elite, Exclusive, Loyalty, Training Community</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>https://tenthousand.cc/products/elite-plus</t>
         </is>
@@ -967,892 +1018,842 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Handle</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Body (HTML)</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Product Category</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Tags</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Option1 Name</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="J1" s="11" t="inlineStr">
         <is>
           <t>Option1 Value</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="K1" s="11" t="inlineStr">
         <is>
           <t>Variant SKU</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="L1" s="11" t="inlineStr">
         <is>
           <t>Variant Grams</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="M1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Tracker</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="N1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Qty</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="O1" s="11" t="inlineStr">
         <is>
           <t>Variant Inventory Policy</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="P1" s="11" t="inlineStr">
         <is>
           <t>Variant Fulfillment Service</t>
         </is>
       </c>
-      <c r="Q1" s="10" t="inlineStr">
+      <c r="Q1" s="11" t="inlineStr">
         <is>
           <t>Variant Price</t>
         </is>
       </c>
-      <c r="R1" s="10" t="inlineStr">
+      <c r="R1" s="11" t="inlineStr">
         <is>
           <t>Variant Compare At Price</t>
         </is>
       </c>
-      <c r="S1" s="10" t="inlineStr">
+      <c r="S1" s="11" t="inlineStr">
         <is>
           <t>Variant Requires Shipping</t>
         </is>
       </c>
-      <c r="T1" s="10" t="inlineStr">
+      <c r="T1" s="11" t="inlineStr">
         <is>
           <t>Variant Taxable</t>
         </is>
       </c>
-      <c r="U1" s="10" t="inlineStr">
+      <c r="U1" s="11" t="inlineStr">
         <is>
           <t>Variant Barcode</t>
         </is>
       </c>
-      <c r="V1" s="10" t="inlineStr">
+      <c r="V1" s="11" t="inlineStr">
         <is>
           <t>Image Src</t>
         </is>
       </c>
-      <c r="W1" s="10" t="inlineStr">
+      <c r="W1" s="11" t="inlineStr">
         <is>
           <t>Image Position</t>
         </is>
       </c>
-      <c r="X1" s="10" t="inlineStr">
+      <c r="X1" s="11" t="inlineStr">
         <is>
           <t>Image Alt Text</t>
         </is>
       </c>
-      <c r="Y1" s="10" t="inlineStr">
+      <c r="Y1" s="11" t="inlineStr">
         <is>
           <t>Gift Card</t>
         </is>
       </c>
-      <c r="Z1" s="10" t="inlineStr">
+      <c r="Z1" s="11" t="inlineStr">
         <is>
           <t>SEO Title</t>
         </is>
       </c>
-      <c r="AA1" s="10" t="inlineStr">
+      <c r="AA1" s="11" t="inlineStr">
         <is>
           <t>SEO Description</t>
         </is>
       </c>
-      <c r="AB1" s="10" t="inlineStr">
+      <c r="AB1" s="11" t="inlineStr">
         <is>
           <t>Google Shopping / Google Product Category</t>
         </is>
       </c>
-      <c r="AC1" s="10" t="inlineStr">
+      <c r="AC1" s="11" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>daily-ripstop-tote</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>Daily Ripstop Tote | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;Daily Ripstop Tote&lt;/strong&gt; by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Tenthousand Cc (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Ten Thousand Daily Ripstop Tote Bag | Durable Gym &amp; Travel Carry</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Engineered for the uncompromising athlete, our Daily Ripstop Tote offers a rugged solution for transporting your gear from the training floor to the office. This versatile bag combines minimalist design with military-grade durability to withstand your toughest daily commutes.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Constructed from high-tenacity, tear-resistant ripstop nylon fabric.&lt;/li&gt;&lt;li&gt;Reinforced stress points ensure maximum load-bearing capacity for gym equipment.&lt;/li&gt;&lt;li&gt;Water-resistant coating protects your belongings from the elements.&lt;/li&gt;&lt;li&gt;Internal organization pockets for secure storage of valuables and small items.&lt;/li&gt;&lt;li&gt;Minimalist aesthetic that seamlessly transitions from gym to city life.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;&lt;p&gt;Material: 100% Ripstop Nylon | Dimensions: Standard Carry | Weight: Lightweight Performance&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
         <is>
           <t>Tenthousand Cc</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G2" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Handbags, Wallets &amp; Cases &gt; Totes</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Handbags, Wallets &amp; Cases &gt; Totes</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>Accessories, Bags, Tote, Gym Gear, Travel, Ripstop</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>DAILY-RIPSTOP-TOTE-FIXED</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M2" s="11" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N2" s="11" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O2" s="11" t="inlineStr">
+      <c r="O2" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P2" s="11" t="inlineStr">
+      <c r="P2" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q2" s="11" t="inlineStr">
+      <c r="Q2" s="12" t="inlineStr">
         <is>
           <t>9800.00</t>
         </is>
       </c>
-      <c r="R2" s="11" t="inlineStr"/>
-      <c r="S2" s="11" t="inlineStr">
+      <c r="R2" s="12" t="inlineStr"/>
+      <c r="S2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T2" s="11" t="inlineStr">
+      <c r="T2" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U2" s="11" t="inlineStr"/>
-      <c r="V2" s="11" t="inlineStr">
+      <c r="U2" s="12" t="inlineStr"/>
+      <c r="V2" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0251/7377/files/ToteBag_1.jpg?v=1792092060</t>
         </is>
       </c>
-      <c r="W2" s="11" t="inlineStr">
+      <c r="W2" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X2" s="11" t="inlineStr">
-        <is>
-          <t>Daily Ripstop Tote - Tenthousand Cc Official Product View</t>
-        </is>
-      </c>
-      <c r="Y2" s="11" t="inlineStr">
+      <c r="X2" s="12" t="inlineStr">
+        <is>
+          <t>Ten Thousand Daily Ripstop Tote bag in black featuring durable fabric and minimalist logo branding.</t>
+        </is>
+      </c>
+      <c r="Y2" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z2" s="11" t="inlineStr">
-        <is>
-          <t>Daily Ripstop Tote | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="AA2" s="11" t="inlineStr">
-        <is>
-          <t>The  Daily Ripstop Tote  by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to e</t>
-        </is>
-      </c>
-      <c r="AB2" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC2" s="11" t="inlineStr">
+      <c r="Z2" s="12" t="inlineStr">
+        <is>
+          <t>Ten Thousand Daily Ripstop Tote Bag | Durable Gym &amp; Travel Carry</t>
+        </is>
+      </c>
+      <c r="AA2" s="12" t="inlineStr">
+        <is>
+          <t>Engineered for the uncompromising athlete, our Daily Ripstop Tote offers a rugged solution for transporting your gear from the training floor to the office</t>
+        </is>
+      </c>
+      <c r="AB2" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Handbags, Wallets &amp; Cases &gt; Totes</t>
+        </is>
+      </c>
+      <c r="AC2" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>core-logo-hat</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Core Logo Hat | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;Core Logo Hat&lt;/strong&gt; by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Tenthousand Cc (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Ten Thousand Core Logo Hat | Performance Training Cap</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Stay focused during high-intensity training sessions with a performance cap designed to manage moisture and keep you cool. The Core Logo Hat combines a sleek, athletic silhouette with breathable materials for all-day comfort.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Moisture-wicking interior sweatband pulls perspiration away from the skin.&lt;/li&gt;&lt;li&gt;Lightweight, breathable crown fabric maximizes airflow during exertion.&lt;/li&gt;&lt;li&gt;Adjustable snapback closure for a customizable, secure fit.&lt;/li&gt;&lt;li&gt;Structure-maintained visor provides consistent coverage and sun protection.&lt;/li&gt;&lt;li&gt;Low-profile design minimizes bulk for an unobtrusive training experience.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;&lt;p&gt;Material: Performance Polyester Blend | Fit: Adjustable Snapback | Design: Low Profile&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>Tenthousand Cc</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing Accessories &gt; Hats</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing Accessories &gt; Hats</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Accessories, Headwear, Hats, Training Gear, Core Collection, Performance</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K3" s="11" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>CORE-LOGO-HAT-FIXED</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N3" s="11" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P3" s="11" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="Q3" s="12" t="inlineStr">
         <is>
           <t>7200.00</t>
         </is>
       </c>
-      <c r="R3" s="11" t="inlineStr"/>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="R3" s="12" t="inlineStr"/>
+      <c r="S3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T3" s="11" t="inlineStr">
+      <c r="T3" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U3" s="11" t="inlineStr"/>
-      <c r="V3" s="11" t="inlineStr">
+      <c r="U3" s="12" t="inlineStr"/>
+      <c r="V3" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0251/7377/files/X_Hat_1.jpg?v=1792091393</t>
         </is>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X3" s="11" t="inlineStr">
-        <is>
-          <t>Core Logo Hat - Tenthousand Cc Official Product View</t>
-        </is>
-      </c>
-      <c r="Y3" s="11" t="inlineStr">
+      <c r="X3" s="12" t="inlineStr">
+        <is>
+          <t>Ten Thousand Core Logo athletic training hat with adjustable snapback and signature branding.</t>
+        </is>
+      </c>
+      <c r="Y3" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z3" s="11" t="inlineStr">
-        <is>
-          <t>Core Logo Hat | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="AA3" s="11" t="inlineStr">
-        <is>
-          <t>The  Core Logo Hat  by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to elimin</t>
-        </is>
-      </c>
-      <c r="AB3" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC3" s="11" t="inlineStr">
+      <c r="Z3" s="12" t="inlineStr">
+        <is>
+          <t>Ten Thousand Core Logo Hat | Performance Training Cap</t>
+        </is>
+      </c>
+      <c r="AA3" s="12" t="inlineStr">
+        <is>
+          <t>Stay focused during high-intensity training sessions with a performance cap designed to manage moisture and keep you cool. The Core Logo Hat combines a sle</t>
+        </is>
+      </c>
+      <c r="AB3" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing Accessories &gt; Hats</t>
+        </is>
+      </c>
+      <c r="AC3" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>tt-bandana</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Cotton Bandana - Kettlebell | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;Cotton Bandana - Kettlebell&lt;/strong&gt; by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Tenthousand Cc (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Ten Thousand Kettlebell Cotton Bandana | Versatile Gym Accessory</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;A classic training staple reimagined, this cotton bandana provides essential moisture management and versatility for every athlete. Whether used to keep sweat at bay or as a quick wrap, its durable construction stands up to daily gym abuse.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Soft, high-quality cotton construction for superior comfort against the skin.&lt;/li&gt;&lt;li&gt;Highly absorbent fabric effectively wicks moisture during heavy lifting.&lt;/li&gt;&lt;li&gt;Multi-functional design serves as a head-tie, wristband, or equipment grip.&lt;/li&gt;&lt;li&gt;Custom Kettlebell graphic print honors the classic training aesthetic.&lt;/li&gt;&lt;li&gt;Easy-care material that withstands repeated washing and intense usage.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;&lt;p&gt;Material: 100% Cotton | Print: Custom Kettlebell Graphic | Size: Standard Square&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Tenthousand Cc</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing Accessories &gt; Bandanas</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing Accessories &gt; Bandanas</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Accessories, Bandana, Kettlebell, Training Essentials, Gym Gear, Limited Edition</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>TT-BANDANA-FIXED</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P4" s="11" t="inlineStr">
+      <c r="P4" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q4" s="11" t="inlineStr">
+      <c r="Q4" s="12" t="inlineStr">
         <is>
           <t>3200.00</t>
         </is>
       </c>
-      <c r="R4" s="11" t="inlineStr"/>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="R4" s="12" t="inlineStr"/>
+      <c r="S4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T4" s="11" t="inlineStr">
+      <c r="T4" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U4" s="11" t="inlineStr"/>
-      <c r="V4" s="11" t="inlineStr">
+      <c r="U4" s="12" t="inlineStr"/>
+      <c r="V4" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0251/7377/files/1bandana.jpg?v=1790362258</t>
         </is>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X4" s="11" t="inlineStr">
-        <is>
-          <t>Cotton Bandana - Kettlebell - Tenthousand Cc Official Product View</t>
-        </is>
-      </c>
-      <c r="Y4" s="11" t="inlineStr">
+      <c r="X4" s="12" t="inlineStr">
+        <is>
+          <t>Ten Thousand cotton bandana featuring a kettlebell print graphic in high-contrast ink.</t>
+        </is>
+      </c>
+      <c r="Y4" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z4" s="11" t="inlineStr">
-        <is>
-          <t>Cotton Bandana - Kettlebell | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="AA4" s="11" t="inlineStr">
-        <is>
-          <t>The  Cotton Bandana - Kettlebell  by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engine</t>
-        </is>
-      </c>
-      <c r="AB4" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC4" s="11" t="inlineStr">
+      <c r="Z4" s="12" t="inlineStr">
+        <is>
+          <t>Ten Thousand Kettlebell Cotton Bandana | Versatile Gym Accessory</t>
+        </is>
+      </c>
+      <c r="AA4" s="12" t="inlineStr">
+        <is>
+          <t>A classic training staple reimagined, this cotton bandana provides essential moisture management and versatility for every athlete. Whether used to keep sw</t>
+        </is>
+      </c>
+      <c r="AB4" s="12" t="inlineStr">
+        <is>
+          <t>Apparel &amp; Accessories &gt; Clothing Accessories &gt; Bandanas</t>
+        </is>
+      </c>
+      <c r="AC4" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>tt-yeti-water-bottle</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>YETI® x Ten Thousand Rambler 36oz | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;YETI® x Ten Thousand Rambler 36oz&lt;/strong&gt; by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Tenthousand Cc (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>YETI x Ten Thousand Rambler 36oz Insulated Water Bottle</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Master your hydration with this premium collaboration bottle, featuring legendary YETI insulation to keep your drinks ice-cold during the most grueling sessions. Built for the rugged athlete, it stands as the ultimate companion for gym training and off-grid exploration.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Double-wall vacuum insulation keeps liquids cold or hot for hours.&lt;/li&gt;&lt;li&gt;18/8 stainless steel construction provides puncture and rust resistance.&lt;/li&gt;&lt;li&gt;No-Sweat™ design keeps your hands dry while the bottle remains cold.&lt;/li&gt;&lt;li&gt;Leak-resistant Chug Cap allows for quick, effortless hydration flow.&lt;/li&gt;&lt;li&gt;Durable dishwasher-safe design makes post-workout cleanup simple.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;&lt;p&gt;Volume: 36 oz | Material: 18/8 Stainless Steel | Compatibility: Dishwasher Safe&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Tenthousand Cc</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Kitchen &amp; Dining &gt; Kitchen Tools &amp; Utensils &gt; Water Bottles</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Kitchen &amp; Dining &gt; Kitchen Tools &amp; Utensils &gt; Water Bottles</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Accessories, Yeti, Hydration, Water Bottle, Gym Gear, Collaboration</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>TT-YETI-WATER-BOTTLE-FIXED</t>
         </is>
       </c>
-      <c r="L5" s="11" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O5" s="11" t="inlineStr">
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P5" s="11" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q5" s="11" t="inlineStr">
+      <c r="Q5" s="12" t="inlineStr">
         <is>
           <t>7700.00</t>
         </is>
       </c>
-      <c r="R5" s="11" t="inlineStr"/>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="R5" s="12" t="inlineStr"/>
+      <c r="S5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T5" s="11" t="inlineStr">
+      <c r="T5" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U5" s="11" t="inlineStr"/>
-      <c r="V5" s="11" t="inlineStr">
+      <c r="U5" s="12" t="inlineStr"/>
+      <c r="V5" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0251/7377/files/YetiBottle_Front.jpg?v=1788136596</t>
         </is>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X5" s="11" t="inlineStr">
-        <is>
-          <t>YETI® x Ten Thousand Rambler 36oz - Tenthousand Cc Official Product View</t>
-        </is>
-      </c>
-      <c r="Y5" s="11" t="inlineStr">
+      <c r="X5" s="12" t="inlineStr">
+        <is>
+          <t>YETI x Ten Thousand Rambler 36oz insulated stainless steel water bottle with co-branded logo.</t>
+        </is>
+      </c>
+      <c r="Y5" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z5" s="11" t="inlineStr">
-        <is>
-          <t>YETI® x Ten Thousand Rambler 36oz | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="AA5" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The  YETI® x Ten Thousand Rambler 36oz  by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully </t>
-        </is>
-      </c>
-      <c r="AB5" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC5" s="11" t="inlineStr">
+      <c r="Z5" s="12" t="inlineStr">
+        <is>
+          <t>YETI x Ten Thousand Rambler 36oz Insulated Water Bottle</t>
+        </is>
+      </c>
+      <c r="AA5" s="12" t="inlineStr">
+        <is>
+          <t>Master your hydration with this premium collaboration bottle, featuring legendary YETI insulation to keep your drinks ice-cold during the most grueling ses</t>
+        </is>
+      </c>
+      <c r="AB5" s="12" t="inlineStr">
+        <is>
+          <t>Home &amp; Garden &gt; Kitchen &amp; Dining &gt; Kitchen Tools &amp; Utensils &gt; Water Bottles</t>
+        </is>
+      </c>
+      <c r="AC5" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>elite-plus</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Black | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The &lt;strong&gt;Black&lt;/strong&gt; by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate compromises, it delivers everyday dependability with refined modern aesthetics.&lt;/p&gt;
-&lt;h3&gt;Key Features &amp; Highlights&lt;/h3&gt;
-&lt;ul style='padding-left:20px; line-height:1.6;'&gt;
-&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Performance Fabric Blend:&lt;/strong&gt; Engineered for superior breathability, natural stretch, and all-day comfort.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Tailored Precision Silhouette:&lt;/strong&gt; Modern athletic profile that transitions seamlessly from office to active wear.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Reinforced Durability:&lt;/strong&gt; Double-needle flatlock stitching on high-stress seams prevents warping and fraying.&lt;/li&gt;&lt;li style='margin-bottom:6px;'&gt;&lt;strong&gt;Pre-Shrunk &amp; Easy Care:&lt;/strong&gt; Maintains original fit, color depth, and soft hand-feel wash after wash.&lt;/li&gt;
-&lt;/ul&gt;
-&lt;h3&gt;Technical Specifications&lt;/h3&gt;
-&lt;table style='width:100%; border-collapse:collapse; margin-top:12px; font-size:14px; text-align:left;'&gt;
-  &lt;tbody&gt;
-&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fabric Composition&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Premium Cotton &amp; Technical Performance Blend&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Fit Profile&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Modern Tailored Silhouette (True to Size)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Care Instructions&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Machine wash cold with like colors, tumble dry low&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Brand Origin&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Tenthousand Cc (United States)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0; font-weight:600; background:#f8fafc; width:35%;'&gt;Craftsmanship&lt;/td&gt;&lt;td style='padding:6px 10px; border:1px solid #e2e8f0;'&gt;Reinforced Seams &amp; Colorfast Finish&lt;/td&gt;&lt;/tr&gt;
-  &lt;/tbody&gt;
-&lt;/table&gt;</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Ten Thousand Elite Plus Membership | Black Tier Benefits</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Unlock the highest level of athletic performance and community access with our exclusive Elite Plus Black Membership. This premium tier is designed for the dedicated athlete seeking priority service and unique member-only advantages.&lt;/p&gt;&lt;h3&gt;Key Features &amp; Benefits&lt;/h3&gt;&lt;ul&gt;&lt;li&gt;Exclusive early access to limited edition product drops and collaborations.&lt;/li&gt;&lt;li&gt;Priority customer service support for all your account needs.&lt;/li&gt;&lt;li&gt;Invitations to private, member-only training events and challenges.&lt;/li&gt;&lt;li&gt;Enhanced benefits across the entire Ten Thousand ecosystem.&lt;/li&gt;&lt;li&gt;Members-only pricing and loyalty rewards for high-frequency training.&lt;/li&gt;&lt;/ul&gt;&lt;div class="specs-summary"&gt;&lt;p&gt;Status: Elite Plus Black | Access: Unlimited Membership | Validity: Annual&lt;/p&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>Tenthousand Cc</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>Apparel, Everyday Wear, Performance Fit, Premium Essentials, Made in USA, Tailored Collection</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Services &gt; Subscriptions &gt; Membership Programs</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Services &gt; Subscriptions &gt; Membership Programs</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Membership, Elite, Exclusive, Loyalty, Training Community</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J6" s="11" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>Default Title</t>
         </is>
       </c>
-      <c r="K6" s="11" t="inlineStr">
+      <c r="K6" s="12" t="inlineStr">
         <is>
           <t>ELITE-PLUS-FIXED</t>
         </is>
       </c>
-      <c r="L6" s="11" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="12" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O6" s="11" t="inlineStr">
+      <c r="O6" s="12" t="inlineStr">
         <is>
           <t>deny</t>
         </is>
       </c>
-      <c r="P6" s="11" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
         <is>
           <t>manual</t>
         </is>
       </c>
-      <c r="Q6" s="11" t="inlineStr">
+      <c r="Q6" s="12" t="inlineStr">
         <is>
           <t>13200.00</t>
         </is>
       </c>
-      <c r="R6" s="11" t="inlineStr"/>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="R6" s="12" t="inlineStr"/>
+      <c r="S6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T6" s="11" t="inlineStr">
+      <c r="T6" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="U6" s="11" t="inlineStr"/>
-      <c r="V6" s="11" t="inlineStr">
+      <c r="U6" s="12" t="inlineStr"/>
+      <c r="V6" s="12" t="inlineStr">
         <is>
           <t>https://cdn.shopify.com/s/files/1/0251/7377/files/tt_membership.svg?v=1790164582</t>
         </is>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X6" s="11" t="inlineStr">
-        <is>
-          <t>Black - Tenthousand Cc Official Product View</t>
-        </is>
-      </c>
-      <c r="Y6" s="11" t="inlineStr">
+      <c r="X6" s="12" t="inlineStr">
+        <is>
+          <t>Ten Thousand Elite Plus membership badge icon for Black tier subscribers.</t>
+        </is>
+      </c>
+      <c r="Y6" s="12" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="Z6" s="11" t="inlineStr">
-        <is>
-          <t>Black | Everyday Performance &amp; Fit</t>
-        </is>
-      </c>
-      <c r="AA6" s="11" t="inlineStr">
-        <is>
-          <t>The  Black  by Tenthousand Cc represents the highest standard of intentional craftsmanship and functional design. Thoughtfully engineered to eliminate comp</t>
-        </is>
-      </c>
-      <c r="AB6" s="11" t="inlineStr">
-        <is>
-          <t>Apparel &amp; Accessories &gt; Clothing</t>
-        </is>
-      </c>
-      <c r="AC6" s="11" t="inlineStr">
+      <c r="Z6" s="12" t="inlineStr">
+        <is>
+          <t>Ten Thousand Elite Plus Membership | Black Tier Benefits</t>
+        </is>
+      </c>
+      <c r="AA6" s="12" t="inlineStr">
+        <is>
+          <t>Unlock the highest level of athletic performance and community access with our exclusive Elite Plus Black Membership. This premium tier is designed for the</t>
+        </is>
+      </c>
+      <c r="AB6" s="12" t="inlineStr">
+        <is>
+          <t>Services &gt; Subscriptions &gt; Membership Programs</t>
+        </is>
+      </c>
+      <c r="AC6" s="12" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
